--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T09:40:11+00:00</t>
+    <t>2025-05-13T09:40:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T09:40:41+00:00</t>
+    <t>2025-05-13T09:51:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T09:51:33+00:00</t>
+    <t>2025-05-13T09:59:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T09:59:34+00:00</t>
+    <t>2025-05-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:03:40+00:00</t>
+    <t>2025-05-13T10:07:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:07:51+00:00</t>
+    <t>2025-05-13T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:11:27+00:00</t>
+    <t>2025-05-13T10:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/nr-add-change-notes/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:16:21+00:00</t>
+    <t>2025-05-13T12:09:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
